--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KKkot\OneDrive\デスクトップ\AtCoder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3B3A49-55A8-4064-BB12-F6837608E7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF5ED3B-42C8-44D0-84EC-0E76DB9FC288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>

--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF5ED3B-42C8-44D0-84EC-0E76DB9FC288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF5D3B9-B42E-42B7-A655-77D153655A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="162">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -2287,6 +2287,156 @@
     </rPh>
     <rPh sb="30" eb="31">
       <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://atcoder.jp/contests/abc419/tasks/abc419_b</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>multiset,priority_queue</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>map&lt;key, 個数&gt;の時に使えるかも。Erase(種類)かerase(イテレータ)で削除の形式が違う。種類だと該当key全部削除、イテレータなら、それだけ削除。Pri_queueは引数なしだと最大値の取得。引数を入れると最小値の取得にできる。</t>
+    <rPh sb="9" eb="11">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ゼンブ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="98" eb="101">
+      <t>サイダイチ</t>
+    </rPh>
+    <rPh sb="102" eb="104">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="108" eb="109">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="112" eb="115">
+      <t>サイショウチ</t>
+    </rPh>
+    <rPh sb="116" eb="118">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://atcoder.jp/contests/abc419/tasks/abc419_c</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>boundning box</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. 真ん中の方に集まればよさそう。2. 四つ角かボトルネックになりそう。3. 8近傍だから、軸は独立して考えていい。4. x,y軸それぞれに対して移動時間は(max-min+1)/2（+1は出発座標と到着座標の偶奇が異なるとき、-なのは中央値（max+min+1）/2 - min）だから。5. x, y軸のmaxを取る。</t>
+    <rPh sb="3" eb="4">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カド</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>キンボウ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ジク</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ドクリツ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ジク</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>シュッパツ</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>ザヒョウ</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>トウチャク</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>ザヒョウ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>グウキ</t>
+    </rPh>
+    <rPh sb="109" eb="110">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="119" eb="122">
+      <t>チュウオウチ</t>
+    </rPh>
+    <rPh sb="153" eb="154">
+      <t>ジク</t>
+    </rPh>
+    <rPh sb="159" eb="160">
+      <t>ト</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2728,7 +2878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BD9036-BF84-4A48-95DA-2ABE8E4C369D}">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="45.09765625" style="1" customWidth="1"/>
@@ -3311,6 +3461,28 @@
       </c>
       <c r="C53" s="1" t="s">
         <v>155</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A55" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A56" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -3366,6 +3538,8 @@
     <hyperlink ref="A51" r:id="rId48" xr:uid="{C6DECF16-AACA-4E16-89E6-8462655E4B70}"/>
     <hyperlink ref="A52" r:id="rId49" xr:uid="{A625AF17-C484-4385-8460-7E8E2B0CE668}"/>
     <hyperlink ref="A53" r:id="rId50" xr:uid="{8599F1EB-34CC-4878-A358-1581D7874B0A}"/>
+    <hyperlink ref="A55" r:id="rId51" xr:uid="{F6DF157D-DF64-4344-B3ED-C18BC94045CF}"/>
+    <hyperlink ref="A56" r:id="rId52" xr:uid="{7D0A6D95-0A62-4DC2-971B-2A5F23A94138}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF5D3B9-B42E-42B7-A655-77D153655A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22203A13-A08B-4688-8E01-59C3F9A7F51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="171">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -2438,6 +2438,144 @@
     <rPh sb="159" eb="160">
       <t>ト</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://atcoder.jp/contests/abc417/tasks/abc417_c</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変数分離</t>
+    <rPh sb="0" eb="4">
+      <t>ヘンスウブンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>iとjを等号の左右別々に分ける。Mapで管理し、順に見ていく。0の管理は制約上不要だった。</t>
+    <rPh sb="4" eb="6">
+      <t>トウゴウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サユウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ベツベツ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>セイヤク</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://atcoder.jp/contests/abc416/tasks/abc416_c</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>再帰、dfs</t>
+    <rPh sb="0" eb="2">
+      <t>サイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>長さK（変数）の数列を全列挙する。</t>
+    <rPh sb="0" eb="1">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>スウレツ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ゼンレッキョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://atcoder.jp/contests/abc416/tasks/abc416_d</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. Aの大きい要素とBの小さい要素をペアにして、できるだけMをギリギリ超すように選べばよさそう。2. Aを降順に見て、足してMを超えるギリギリのBの要素をにぶたん。Bからその要素を削除（mulisetが活きる）3. ansはAとBの全要素の和-M*ペアにできた個数。</t>
+    <rPh sb="5" eb="6">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>チイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>エラ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>コウジュン</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="102" eb="103">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="117" eb="120">
+      <t>ゼンヨウソ</t>
+    </rPh>
+    <rPh sb="121" eb="122">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>コスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>multiset greater</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2878,7 +3016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BD9036-BF84-4A48-95DA-2ABE8E4C369D}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="45.09765625" style="1" customWidth="1"/>
@@ -3483,6 +3621,39 @@
       </c>
       <c r="C56" s="1" t="s">
         <v>161</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A57" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A58" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A59" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3540,6 +3711,9 @@
     <hyperlink ref="A53" r:id="rId50" xr:uid="{8599F1EB-34CC-4878-A358-1581D7874B0A}"/>
     <hyperlink ref="A55" r:id="rId51" xr:uid="{F6DF157D-DF64-4344-B3ED-C18BC94045CF}"/>
     <hyperlink ref="A56" r:id="rId52" xr:uid="{7D0A6D95-0A62-4DC2-971B-2A5F23A94138}"/>
+    <hyperlink ref="A57" r:id="rId53" xr:uid="{471EF17D-E3CC-498A-827A-870E2CBEAB71}"/>
+    <hyperlink ref="A58" r:id="rId54" xr:uid="{ABBD6725-25BD-4A1E-AF64-8427414B1E2B}"/>
+    <hyperlink ref="A59" r:id="rId55" xr:uid="{FF986D66-1472-4136-99AF-EE7569D6BE4D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22203A13-A08B-4688-8E01-59C3F9A7F51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E5DECF-5984-4EB3-9412-1938917961E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="177">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -2576,6 +2576,102 @@
   </si>
   <si>
     <t>multiset greater</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://atcoder.jp/contests/abc420/tasks/abc420_e</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dsu、代表元</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クエリ3で黒頂点の全探索が間に合わない。Leaderに対して連結成分内の黒の個数を管理すればクエリ3がO(1)でできる。</t>
+    <rPh sb="5" eb="6">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウテン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ゼンタンサク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>レンケツ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>セイブン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://atcoder.jp/contests/abc420/tasks/abc420_d</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BFS、世界の拡張</t>
+    <rPh sb="4" eb="6">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BFSのdist配列を3次元にし、スイッチを偶数回押したときと奇数回のときの最短距離を格納する（世界は2つの状態のどちらかしか存在しない）。Grid配列の妥当性チェック（範囲外じゃないかとか）ははじめにやる。状態（今回でいえばスイッチを押した回数の偶奇）の変更をそのあとやり、訪問済みかのチェックを行う。</t>
+    <rPh sb="8" eb="10">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジゲン</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>グウスウカイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>キスウカイ</t>
+    </rPh>
+    <rPh sb="38" eb="42">
+      <t>サイタンキョリ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>カクノウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ソンザイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3016,7 +3112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BD9036-BF84-4A48-95DA-2ABE8E4C369D}">
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="45.09765625" style="1" customWidth="1"/>
@@ -3654,6 +3750,28 @@
       </c>
       <c r="C59" s="1" t="s">
         <v>169</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A60" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A61" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -3714,6 +3832,8 @@
     <hyperlink ref="A57" r:id="rId53" xr:uid="{471EF17D-E3CC-498A-827A-870E2CBEAB71}"/>
     <hyperlink ref="A58" r:id="rId54" xr:uid="{ABBD6725-25BD-4A1E-AF64-8427414B1E2B}"/>
     <hyperlink ref="A59" r:id="rId55" xr:uid="{FF986D66-1472-4136-99AF-EE7569D6BE4D}"/>
+    <hyperlink ref="A60" r:id="rId56" xr:uid="{826366C9-20C1-471A-B32F-96154E89C987}"/>
+    <hyperlink ref="A61" r:id="rId57" xr:uid="{9961145C-6734-4DE8-A33C-F4F48BC88C3F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E5DECF-5984-4EB3-9412-1938917961E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1F82E6-51CC-44CD-BDCD-93F714D9833C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="180">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -2671,6 +2671,75 @@
     </rPh>
     <rPh sb="63" eb="65">
       <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://atcoder.jp/contests/abc414/tasks/abc414_c</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回文判定</t>
+    <rPh sb="0" eb="2">
+      <t>カイブン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10進数の回文→奇数桁と偶数桁で場合分けして前半の数を全探索し、reverseしたものと連結させることで探索可能（1桁の数に注意）。回文かどうかの判定はテンプレを用意しておくといい。</t>
+    <rPh sb="2" eb="4">
+      <t>シンスウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイブン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>キスウケタ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>グウスウケタ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>バアイワ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ゼンハン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>ゼンタンサク</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>レンケツ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>タンサク</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ケタ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>チュウイ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>カイブン</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>ヨウイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3112,7 +3181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BD9036-BF84-4A48-95DA-2ABE8E4C369D}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="45.09765625" style="1" customWidth="1"/>
@@ -3772,6 +3841,17 @@
       </c>
       <c r="C61" s="1" t="s">
         <v>176</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A62" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -3834,6 +3914,7 @@
     <hyperlink ref="A59" r:id="rId55" xr:uid="{FF986D66-1472-4136-99AF-EE7569D6BE4D}"/>
     <hyperlink ref="A60" r:id="rId56" xr:uid="{826366C9-20C1-471A-B32F-96154E89C987}"/>
     <hyperlink ref="A61" r:id="rId57" xr:uid="{9961145C-6734-4DE8-A33C-F4F48BC88C3F}"/>
+    <hyperlink ref="A62" r:id="rId58" xr:uid="{701B9719-D750-4E47-B839-00E70E39088C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1F82E6-51CC-44CD-BDCD-93F714D9833C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D76110-C949-4080-B02F-8BEE0866D2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>

--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D76110-C949-4080-B02F-8BEE0866D2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BA1219-FDE7-4A0F-9EDB-8AE26C9A6C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="183">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -2740,6 +2740,78 @@
     </rPh>
     <rPh sb="81" eb="83">
       <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://atcoder.jp/contests/abc413/tasks/abc413_d</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>絶対値順のソート、等比数列</t>
+    <rPh sb="0" eb="3">
+      <t>ゼッタイチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>トウヒ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>スウレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基本的な等比数列の判定は絶対値順にソートしてAi*Ai+2==Ai+1^2。公比が1,-1の場合を忘れないように。また、今回は公比0や数列に0が含まれる場合がなかったが、その点を気を付ける必要あり。</t>
+    <rPh sb="0" eb="3">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ゼッタイチ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>コウヒ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ワス</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>コウヒ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>スウレツ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="89" eb="90">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="91" eb="92">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>ヒツヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3181,7 +3253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BD9036-BF84-4A48-95DA-2ABE8E4C369D}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="45.09765625" style="1" customWidth="1"/>
@@ -3852,6 +3924,17 @@
       </c>
       <c r="C62" s="1" t="s">
         <v>179</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A63" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -3915,6 +3998,7 @@
     <hyperlink ref="A60" r:id="rId56" xr:uid="{826366C9-20C1-471A-B32F-96154E89C987}"/>
     <hyperlink ref="A61" r:id="rId57" xr:uid="{9961145C-6734-4DE8-A33C-F4F48BC88C3F}"/>
     <hyperlink ref="A62" r:id="rId58" xr:uid="{701B9719-D750-4E47-B839-00E70E39088C}"/>
+    <hyperlink ref="A63" r:id="rId59" xr:uid="{A09CA4D1-A76E-4A9B-9BC2-553C1D370048}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BA1219-FDE7-4A0F-9EDB-8AE26C9A6C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5388C392-9ED3-4A9D-909D-FBFF13C60373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="185">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -2812,6 +2812,95 @@
     </rPh>
     <rPh sb="94" eb="96">
       <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://atcoder.jp/contests/abc422/tasks/abc422_d</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>余りを満遍なく配置が難しい。問題から再帰を連想できればok。問題操作をするには数列を構成する必要があるから、逆に要素がKの数列から初めて2つに分割する。このときK/2とK-K/2とすると奇数の時も考えられてよい。配列を配列に代入しても2^Nの計算量であればコピーが間に合うため用いてよい。</t>
+    <rPh sb="0" eb="1">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>マンベン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サイキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>レンソウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>スウレツ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ギャク</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>スウレツ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ブンカツ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>キスウ</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="98" eb="99">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>ダイニュウ</t>
+    </rPh>
+    <rPh sb="121" eb="124">
+      <t>ケイサンリョウ</t>
+    </rPh>
+    <rPh sb="132" eb="133">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="134" eb="135">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="138" eb="139">
+      <t>モチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3253,7 +3342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BD9036-BF84-4A48-95DA-2ABE8E4C369D}">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="45.09765625" style="1" customWidth="1"/>
@@ -3935,6 +4024,17 @@
       </c>
       <c r="C63" s="1" t="s">
         <v>182</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A64" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -3999,6 +4099,7 @@
     <hyperlink ref="A61" r:id="rId57" xr:uid="{9961145C-6734-4DE8-A33C-F4F48BC88C3F}"/>
     <hyperlink ref="A62" r:id="rId58" xr:uid="{701B9719-D750-4E47-B839-00E70E39088C}"/>
     <hyperlink ref="A63" r:id="rId59" xr:uid="{A09CA4D1-A76E-4A9B-9BC2-553C1D370048}"/>
+    <hyperlink ref="A64" r:id="rId60" xr:uid="{66A99996-2ABE-4B8D-96F0-3E04A4A251FB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5388C392-9ED3-4A9D-909D-FBFF13C60373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F063B5A-052C-412C-9363-63DC1A54BE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>

--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F063B5A-052C-412C-9363-63DC1A54BE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027A91B5-A1EA-46C4-B0FB-3D78475230A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="188">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -2901,6 +2902,87 @@
     </rPh>
     <rPh sb="138" eb="139">
       <t>モチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://atcoder.jp/contests/abc402/tasks/abc402_c</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>差分更新、写像を逆に見る</t>
+    <rPh sb="0" eb="4">
+      <t>サブンコウシン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シャゾウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ギャク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すでに克服した料理に関しては今後も克服したままだから、新たに克服する料理にのみ着目する。問題では料理-&gt;食材の情報が与えられるが、食材-&gt;料理のリストを作成することで計算量を削減できる。</t>
+    <rPh sb="3" eb="5">
+      <t>コクフク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>リョウリ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コンゴ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コクフク</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>コクフク</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>リョウリ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>チャクモク</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>リョウリ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ショクザイ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ショクザイ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>リョウリ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="83" eb="86">
+      <t>ケイサンリョウ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>サクゲン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3342,7 +3424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BD9036-BF84-4A48-95DA-2ABE8E4C369D}">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="45.09765625" style="1" customWidth="1"/>
@@ -4035,6 +4117,17 @@
       </c>
       <c r="C64" s="1" t="s">
         <v>184</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A65" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -4100,6 +4193,7 @@
     <hyperlink ref="A62" r:id="rId58" xr:uid="{701B9719-D750-4E47-B839-00E70E39088C}"/>
     <hyperlink ref="A63" r:id="rId59" xr:uid="{A09CA4D1-A76E-4A9B-9BC2-553C1D370048}"/>
     <hyperlink ref="A64" r:id="rId60" xr:uid="{66A99996-2ABE-4B8D-96F0-3E04A4A251FB}"/>
+    <hyperlink ref="A65" r:id="rId61" xr:uid="{5EEAAB89-68BF-4ED8-9FDC-6B6DDF9E4603}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027A91B5-A1EA-46C4-B0FB-3D78475230A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA14D4D-0B45-4E5B-9A5A-E49C40F0D2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="191">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -2984,6 +2983,23 @@
     <rPh sb="87" eb="89">
       <t>サクゲン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://atcoder.jp/contests/abc425/tasks/abc425_b</t>
+  </si>
+  <si>
+    <t>next_permutation、順列全探索</t>
+    <rPh sb="17" eb="19">
+      <t>ジュンレツ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>ゼンタンサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソートする！</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3424,7 +3440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BD9036-BF84-4A48-95DA-2ABE8E4C369D}">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="45.09765625" style="1" customWidth="1"/>
@@ -4128,6 +4144,17 @@
       </c>
       <c r="C65" s="1" t="s">
         <v>187</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A66" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -4196,5 +4223,6 @@
     <hyperlink ref="A65" r:id="rId61" xr:uid="{5EEAAB89-68BF-4ED8-9FDC-6B6DDF9E4603}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId62"/>
 </worksheet>
 </file>
--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA14D4D-0B45-4E5B-9A5A-E49C40F0D2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1F89FF-2F8B-4B0C-8D26-313C60E0B300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>
@@ -2986,9 +2986,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>https://atcoder.jp/contests/abc425/tasks/abc425_b</t>
-  </si>
-  <si>
     <t>next_permutation、順列全探索</t>
     <rPh sb="17" eb="19">
       <t>ジュンレツ</t>
@@ -3000,6 +2997,10 @@
   </si>
   <si>
     <t>ソートする！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://atcoder.jp/contests/abc425/tasks/abc425_b</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4147,14 +4148,14 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -4221,8 +4222,9 @@
     <hyperlink ref="A63" r:id="rId59" xr:uid="{A09CA4D1-A76E-4A9B-9BC2-553C1D370048}"/>
     <hyperlink ref="A64" r:id="rId60" xr:uid="{66A99996-2ABE-4B8D-96F0-3E04A4A251FB}"/>
     <hyperlink ref="A65" r:id="rId61" xr:uid="{5EEAAB89-68BF-4ED8-9FDC-6B6DDF9E4603}"/>
+    <hyperlink ref="A66" r:id="rId62" xr:uid="{42C005A6-F90E-4357-8CF8-5BF94E243029}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId62"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId63"/>
 </worksheet>
 </file>
--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1F89FF-2F8B-4B0C-8D26-313C60E0B300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59AFB5F4-2D72-4F92-87FF-FF926AF023FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3054,12 +3055,30 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -3090,7 +3109,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3100,11 +3119,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3460,184 +3506,186 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C10" s="1" t="s">
+    <row r="10" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:3" s="9" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:3" s="9" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:3" s="9" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="8" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3652,14 +3700,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="8" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3696,14 +3744,14 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="8" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3729,14 +3777,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="12" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3956,7 +4004,7 @@
       <c r="B47" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="3" t="s">
         <v>137</v>
       </c>
     </row>
@@ -3978,7 +4026,7 @@
       <c r="B49" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="3" t="s">
         <v>143</v>
       </c>
     </row>

--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59AFB5F4-2D72-4F92-87FF-FF926AF023FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F3D4B4-EDE8-4487-83CD-DDE5B23AFB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3689,14 +3688,14 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="8" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3711,36 +3710,36 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="12" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3755,25 +3754,25 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="8" t="s">
         <v>75</v>
       </c>
     </row>
@@ -3788,190 +3787,190 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="8" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="8" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="8" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="8" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="8" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="8" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A40" s="2" t="s">
+    <row r="40" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="8" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A41" s="2" t="s">
+    <row r="41" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="8" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A42" s="2" t="s">
+    <row r="42" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="8" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A43" s="2" t="s">
+    <row r="43" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A44" s="2" t="s">
+    <row r="44" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="12" t="s">
         <v>128</v>
       </c>
     </row>
@@ -4008,14 +4007,14 @@
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A48" s="2" t="s">
+    <row r="48" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="8" t="s">
         <v>140</v>
       </c>
     </row>
@@ -4052,14 +4051,14 @@
         <v>149</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A52" s="2" t="s">
+    <row r="52" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="8" t="s">
         <v>150</v>
       </c>
     </row>
@@ -4074,36 +4073,36 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A55" s="2" t="s">
+    <row r="55" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="8" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="8" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A57" s="2" t="s">
+    <row r="57" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="8" t="s">
         <v>164</v>
       </c>
     </row>
@@ -4195,14 +4194,14 @@
         <v>187</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A66" s="2" t="s">
+    <row r="66" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="8" t="s">
         <v>189</v>
       </c>
     </row>

--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F3D4B4-EDE8-4487-83CD-DDE5B23AFB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF2D8E3-FC8E-48F8-BD23-71A2E3296872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>
@@ -2164,46 +2164,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Aをi人分作ると固定すればそれはQmaxまでの全探索。全材料についてAをi人分作れるか、作れるならBは最大何人分つくれるのか。その和のmaxを求める「</t>
-    <rPh sb="3" eb="5">
-      <t>ニンブン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>コテイ</t>
-    </rPh>
-    <rPh sb="23" eb="26">
-      <t>ゼンタンサク</t>
-    </rPh>
-    <rPh sb="27" eb="30">
-      <t>ゼンザイリョウ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ニンブン</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>サイダイ</t>
-    </rPh>
-    <rPh sb="53" eb="56">
-      <t>ナンニンブン</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="71" eb="72">
-      <t>モト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>https://atcoder.jp/contests/abc412/tasks/abc412_c</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3001,6 +2961,46 @@
   </si>
   <si>
     <t>https://atcoder.jp/contests/abc425/tasks/abc425_b</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Aをi人分作ると固定すればそれはQmaxまでの全探索。全材料についてAをi人分作れるか、作れるならBは最大何人分つくれるのか。その和のmaxを求める</t>
+    <rPh sb="3" eb="5">
+      <t>ニンブン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ゼンタンサク</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>ゼンザイリョウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ニンブン</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="53" eb="56">
+      <t>ナンニンブン</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>モト</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3486,7 +3486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BD9036-BF84-4A48-95DA-2ABE8E4C369D}">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="45.09765625" style="1" customWidth="1"/>
@@ -3974,25 +3974,25 @@
         <v>128</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A45" s="2" t="s">
+    <row r="45" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A46" s="2" t="s">
+    <row r="46" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="8" t="s">
         <v>134</v>
       </c>
     </row>
@@ -4029,180 +4029,180 @@
         <v>143</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A50" s="2" t="s">
+    <row r="50" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="7" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A51" s="2" t="s">
+      <c r="B51" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="8" t="s">
         <v>148</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A52" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C53" s="1" t="s">
+    </row>
+    <row r="54" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="7" t="s">
         <v>155</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A55" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A56" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A57" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A60" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B60" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C60" s="1" t="s">
+    </row>
+    <row r="60" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="7" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A61" s="2" t="s">
+      <c r="B60" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C60" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C61" s="1" t="s">
+    </row>
+    <row r="61" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="11" t="s">
         <v>176</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A65" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B65" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C65" s="1" t="s">
+    </row>
+    <row r="65" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B65" s="8" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A66" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B66" s="8" t="s">
+      <c r="C65" s="8" t="s">
         <v>188</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -4258,18 +4258,18 @@
     <hyperlink ref="A51" r:id="rId48" xr:uid="{C6DECF16-AACA-4E16-89E6-8462655E4B70}"/>
     <hyperlink ref="A52" r:id="rId49" xr:uid="{A625AF17-C484-4385-8460-7E8E2B0CE668}"/>
     <hyperlink ref="A53" r:id="rId50" xr:uid="{8599F1EB-34CC-4878-A358-1581D7874B0A}"/>
-    <hyperlink ref="A55" r:id="rId51" xr:uid="{F6DF157D-DF64-4344-B3ED-C18BC94045CF}"/>
-    <hyperlink ref="A56" r:id="rId52" xr:uid="{7D0A6D95-0A62-4DC2-971B-2A5F23A94138}"/>
-    <hyperlink ref="A57" r:id="rId53" xr:uid="{471EF17D-E3CC-498A-827A-870E2CBEAB71}"/>
-    <hyperlink ref="A58" r:id="rId54" xr:uid="{ABBD6725-25BD-4A1E-AF64-8427414B1E2B}"/>
-    <hyperlink ref="A59" r:id="rId55" xr:uid="{FF986D66-1472-4136-99AF-EE7569D6BE4D}"/>
-    <hyperlink ref="A60" r:id="rId56" xr:uid="{826366C9-20C1-471A-B32F-96154E89C987}"/>
-    <hyperlink ref="A61" r:id="rId57" xr:uid="{9961145C-6734-4DE8-A33C-F4F48BC88C3F}"/>
-    <hyperlink ref="A62" r:id="rId58" xr:uid="{701B9719-D750-4E47-B839-00E70E39088C}"/>
-    <hyperlink ref="A63" r:id="rId59" xr:uid="{A09CA4D1-A76E-4A9B-9BC2-553C1D370048}"/>
-    <hyperlink ref="A64" r:id="rId60" xr:uid="{66A99996-2ABE-4B8D-96F0-3E04A4A251FB}"/>
-    <hyperlink ref="A65" r:id="rId61" xr:uid="{5EEAAB89-68BF-4ED8-9FDC-6B6DDF9E4603}"/>
-    <hyperlink ref="A66" r:id="rId62" xr:uid="{42C005A6-F90E-4357-8CF8-5BF94E243029}"/>
+    <hyperlink ref="A54" r:id="rId51" xr:uid="{F6DF157D-DF64-4344-B3ED-C18BC94045CF}"/>
+    <hyperlink ref="A55" r:id="rId52" xr:uid="{7D0A6D95-0A62-4DC2-971B-2A5F23A94138}"/>
+    <hyperlink ref="A56" r:id="rId53" xr:uid="{471EF17D-E3CC-498A-827A-870E2CBEAB71}"/>
+    <hyperlink ref="A57" r:id="rId54" xr:uid="{ABBD6725-25BD-4A1E-AF64-8427414B1E2B}"/>
+    <hyperlink ref="A58" r:id="rId55" xr:uid="{FF986D66-1472-4136-99AF-EE7569D6BE4D}"/>
+    <hyperlink ref="A59" r:id="rId56" xr:uid="{826366C9-20C1-471A-B32F-96154E89C987}"/>
+    <hyperlink ref="A60" r:id="rId57" xr:uid="{9961145C-6734-4DE8-A33C-F4F48BC88C3F}"/>
+    <hyperlink ref="A61" r:id="rId58" xr:uid="{701B9719-D750-4E47-B839-00E70E39088C}"/>
+    <hyperlink ref="A62" r:id="rId59" xr:uid="{A09CA4D1-A76E-4A9B-9BC2-553C1D370048}"/>
+    <hyperlink ref="A63" r:id="rId60" xr:uid="{66A99996-2ABE-4B8D-96F0-3E04A4A251FB}"/>
+    <hyperlink ref="A64" r:id="rId61" xr:uid="{5EEAAB89-68BF-4ED8-9FDC-6B6DDF9E4603}"/>
+    <hyperlink ref="A65" r:id="rId62" xr:uid="{42C005A6-F90E-4357-8CF8-5BF94E243029}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId63"/>

--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF2D8E3-FC8E-48F8-BD23-71A2E3296872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9F04D0-A56C-471A-94B3-907F736B8F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/AtCoder.xlsx
+++ b/AtCoder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AtCoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9F04D0-A56C-471A-94B3-907F736B8F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83FDD93-1546-43E7-9668-7A8368C608D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B9CC3CCD-5E79-4389-A42B-68AFAFE5B83F}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3109,18 +3108,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -3151,6 +3144,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3506,703 +3502,703 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8" t="s">
+    <row r="10" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="9" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:3" s="7" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="9" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:3" s="7" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="9" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:3" s="7" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="11" t="s">
+    <row r="23" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="10" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="11" t="s">
+    <row r="27" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="11" t="s">
+    <row r="30" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="11" t="s">
+    <row r="32" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="10" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="6" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="8" t="s">
+    <row r="35" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="6" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="7" t="s">
+    <row r="38" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="7" t="s">
+    <row r="39" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="6" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="7" t="s">
+    <row r="40" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="7" t="s">
+    <row r="41" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="7" t="s">
+    <row r="42" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="7" t="s">
+    <row r="43" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="6" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="11" t="s">
+    <row r="44" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="10" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="45" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="7" t="s">
+    <row r="45" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="7" t="s">
+    <row r="46" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="6" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="162" x14ac:dyDescent="0.45">
-      <c r="A47" s="2" t="s">
+    <row r="47" spans="1:3" s="7" customFormat="1" ht="162" x14ac:dyDescent="0.45">
+      <c r="A47" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="7" t="s">
+    <row r="48" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="6" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="72" x14ac:dyDescent="0.45">
-      <c r="A49" s="2" t="s">
+    <row r="49" spans="1:3" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.45">
+      <c r="A49" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="12" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="50" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="11" t="s">
+    <row r="50" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="10" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="51" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="7" t="s">
+    <row r="51" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="6" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="7" t="s">
+    <row r="52" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="6" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A53" s="2" t="s">
+    <row r="53" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="6" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="54" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="7" t="s">
+    <row r="54" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="6" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="55" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A55" s="7" t="s">
+    <row r="55" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="6" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="56" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="7" t="s">
+    <row r="56" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="6" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="57" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="7" t="s">
+    <row r="57" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="6" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A58" s="2" t="s">
+    <row r="58" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A59" s="2" t="s">
+    <row r="59" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="6" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="60" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="7" t="s">
+    <row r="60" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="6" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="61" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="11" t="s">
+    <row r="61" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="10" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A62" s="2" t="s">
+    <row r="62" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="6" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A63" s="2" t="s">
+    <row r="63" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="6" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A64" s="2" t="s">
+    <row r="64" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="6" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="65" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="7" t="s">
+    <row r="65" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="6" t="s">
         <v>188</v>
       </c>
     </row>
